--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>127128568</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>127128762</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127134155</v>
       </c>
       <c r="B7" t="n">
-        <v>80143</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127128628</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127134157</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>127134156</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111350848</v>
+        <v>111350854</v>
       </c>
       <c r="B2" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596797.2063237124</v>
+        <v>596757</v>
       </c>
       <c r="R2" t="n">
-        <v>6985887.021071788</v>
+        <v>6985961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111350850</v>
+        <v>111350847</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596771.1170920485</v>
+        <v>596781</v>
       </c>
       <c r="R3" t="n">
-        <v>6985906.711755162</v>
+        <v>6985771</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111350851</v>
+        <v>111350850</v>
       </c>
       <c r="B4" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596771.1170920485</v>
+        <v>596771</v>
       </c>
       <c r="R4" t="n">
-        <v>6985906.711755162</v>
+        <v>6985907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128568</v>
+        <v>127134157</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596775</v>
+        <v>596760</v>
       </c>
       <c r="R5" t="n">
-        <v>6985882</v>
+        <v>6985876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128762</v>
+        <v>111350852</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häbbersjöberget, Jmt</t>
+          <t>Risåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596869</v>
+        <v>596757</v>
       </c>
       <c r="R6" t="n">
-        <v>6985816</v>
+        <v>6985961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127134155</v>
+        <v>127128568</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596737</v>
+        <v>596775</v>
       </c>
       <c r="R7" t="n">
-        <v>6985864</v>
+        <v>6985882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128628</v>
+        <v>127128762</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Risåsen, Jmt</t>
+          <t>Häbbersjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596805</v>
+        <v>596869</v>
       </c>
       <c r="R8" t="n">
-        <v>6985883</v>
+        <v>6985816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127134157</v>
+        <v>127134156</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596760</v>
+        <v>596735</v>
       </c>
       <c r="R9" t="n">
-        <v>6985876</v>
+        <v>6985863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Med fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127134156</v>
+        <v>111350853</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596735</v>
+        <v>596757</v>
       </c>
       <c r="R10" t="n">
-        <v>6985863</v>
+        <v>6985961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,17 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med fruktkroppar</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,15 +1541,413 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127134155</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596737</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985864</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111350848</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596797</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6985887</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127128628</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596805</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6985883</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111350851</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596771</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6985907</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19402-2025 artfynd.xlsx
+++ b/artfynd/A 19402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350854</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350847</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134157</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350852</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128762</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134156</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350853</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127134155</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350848</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127128628</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,8 +2013,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>